--- a/test_inbound3.xlsx
+++ b/test_inbound3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\warehouse_mgr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{287EAFB8-3B06-42F8-B13E-A173C218423B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F586F68-CD17-481F-BE12-FD8994AD2435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A48A8ABB-CF4D-4D2F-97BA-E472414F5723}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="36">
   <si>
     <t>到貨日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,7 +83,59 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1769-ASCII</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>倉庫右側</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1769-CRL3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1769-OF4CI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1769-IQ32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1769-OB32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1769-IF18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>供應商</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所羅門股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普得企業股份有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Schneider</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MGPM-8330</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔡培君</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1E右側</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -488,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1DEB820-F7AC-4A8C-99B5-D02FB059DDD1}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -503,7 +555,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -529,117 +581,117 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46181</v>
+        <v>46133</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>11</v>
+      </c>
+      <c r="I2">
+        <v>20260320004</v>
+      </c>
+      <c r="J2" t="s">
         <v>12</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46181</v>
+        <v>46133</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
       <c r="G3">
-        <v>1</v>
+        <v>104</v>
+      </c>
+      <c r="I3">
+        <v>20260320004</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46181</v>
+        <v>46133</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>184</v>
+      </c>
+      <c r="I4">
+        <v>20260320004</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>46181</v>
+        <v>46133</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>780</v>
+      </c>
+      <c r="I5">
+        <v>20260320004</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>46181</v>
+        <v>46133</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -647,40 +699,225 @@
       <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
       <c r="G6">
-        <v>1</v>
+        <v>659</v>
+      </c>
+      <c r="I6">
+        <v>20260320004</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7">
+        <v>42</v>
+      </c>
+      <c r="I7">
+        <v>20260320004</v>
+      </c>
+      <c r="J7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>50</v>
+      </c>
+      <c r="H8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8">
+        <v>20260326003</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>46181</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
-      <c r="J7" t="s">
-        <v>15</v>
+      <c r="J9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/test_inbound3.xlsx
+++ b/test_inbound3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\warehouse_mgr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F586F68-CD17-481F-BE12-FD8994AD2435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D1E164-EB9C-4CD5-AAB0-327253922443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A48A8ABB-CF4D-4D2F-97BA-E472414F5723}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="52">
   <si>
     <t>到貨日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,10 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>產品名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>序號</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -174,13 +170,69 @@
   </si>
   <si>
     <t>SN:CD208A0T26200006</t>
+  </si>
+  <si>
+    <t>料件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>J115-05-192</t>
+  </si>
+  <si>
+    <t>1756-EN2TR</t>
+  </si>
+  <si>
+    <t>1756-RM2</t>
+  </si>
+  <si>
+    <t>1756-RMC1</t>
+  </si>
+  <si>
+    <t>1756-A17</t>
+  </si>
+  <si>
+    <t>1756-IB32</t>
+  </si>
+  <si>
+    <t>1756-OB32</t>
+  </si>
+  <si>
+    <t>1756-IF16</t>
+  </si>
+  <si>
+    <t>1756-OF8</t>
+  </si>
+  <si>
+    <t>1756-TBCH</t>
+  </si>
+  <si>
+    <t>1756-N2</t>
+  </si>
+  <si>
+    <t>1769-IQ32</t>
+  </si>
+  <si>
+    <t>類型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新竹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台南辦公室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -195,6 +247,13 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體-ExtB"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -219,12 +278,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,384 +602,717 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1DEB820-F7AC-4A8C-99B5-D02FB059DDD1}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="10" max="10" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
       <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46133</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
+      <c r="B2" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2">
         <v>11</v>
       </c>
-      <c r="G2">
+      <c r="J2">
+        <v>20260320004</v>
+      </c>
+      <c r="L2" t="s">
         <v>11</v>
       </c>
-      <c r="I2">
-        <v>20260320004</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46133</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
+      <c r="B3" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3">
         <v>104</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>20260320004</v>
       </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46133</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
+      <c r="B4" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4">
         <v>184</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>20260320004</v>
       </c>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46133</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
+      <c r="B5" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5">
         <v>780</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>20260320004</v>
       </c>
-      <c r="J5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46133</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
+      <c r="B6" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6">
         <v>659</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>20260320004</v>
       </c>
-      <c r="J6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46133</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
+      <c r="B7" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7">
         <v>42</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>20260320004</v>
       </c>
-      <c r="J7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46135</v>
       </c>
-      <c r="B8" t="s">
-        <v>9</v>
+      <c r="B8" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>21</v>
       </c>
-      <c r="E8" t="s">
+      <c r="H8">
+        <v>50</v>
+      </c>
+      <c r="I8" t="s">
         <v>22</v>
       </c>
-      <c r="G8">
-        <v>50</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="J8">
+        <v>20260326003</v>
+      </c>
+      <c r="L8" t="s">
         <v>23</v>
       </c>
-      <c r="I8">
-        <v>20260326003</v>
-      </c>
-      <c r="J8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46181</v>
       </c>
-      <c r="B9" t="s">
-        <v>9</v>
+      <c r="B9" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
         <v>27</v>
       </c>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46181</v>
       </c>
-      <c r="B10" t="s">
-        <v>9</v>
+      <c r="B10" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" t="s">
         <v>29</v>
       </c>
-      <c r="F10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10">
+      <c r="H10">
         <v>1</v>
       </c>
-      <c r="J10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46181</v>
       </c>
-      <c r="B11" t="s">
-        <v>9</v>
+      <c r="B11" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11">
+        <v>28</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11">
         <v>1</v>
       </c>
-      <c r="J11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46181</v>
       </c>
-      <c r="B12" t="s">
-        <v>9</v>
+      <c r="B12" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12">
         <v>1</v>
       </c>
-      <c r="J12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46181</v>
       </c>
-      <c r="B13" t="s">
-        <v>9</v>
+      <c r="B13" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13">
+        <v>28</v>
+      </c>
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13">
         <v>1</v>
       </c>
-      <c r="J13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46181</v>
       </c>
-      <c r="B14" t="s">
-        <v>9</v>
+      <c r="B14" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
         <v>34</v>
       </c>
-      <c r="F14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14">
+      <c r="H14">
         <v>1</v>
       </c>
-      <c r="J14" t="s">
-        <v>28</v>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="33" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="33" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2">
+        <v>25</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2">
+        <v>79</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2">
+        <v>41</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2">
+        <v>6</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="2">
+        <v>310</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="2">
+        <v>129</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="2">
+        <v>9</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
